--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,25 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guiliberali/Documents/GitHub/Learning-from-Big-Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guiliberali/Library/Mobile Documents/com~apple~CloudDocs/Teaching /Teaching - BigData/Teach_BigData 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD047B14-31DE-444B-871C-997410C7FA4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B8B5798-C910-044E-8D21-D32AAE337C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" xr2:uid="{16787138-0C24-184A-98B2-327E13C17B03}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17480" xr2:uid="{16787138-0C24-184A-98B2-327E13C17B03}"/>
   </bookViews>
   <sheets>
-    <sheet name="COMPLETE" sheetId="2" r:id="rId1"/>
-    <sheet name="partial details" sheetId="1" r:id="rId2"/>
+    <sheet name="schedule" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'partial details'!$A$1:$F$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">schedule!$A$1:$F$33</definedName>
   </definedNames>
-  <calcPr calcId="181029" iterateCount="0" calcOnSave="0" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
   <si>
     <t>Monday</t>
   </si>
@@ -105,21 +104,9 @@
     <t>Lecture 2.5</t>
   </si>
   <si>
-    <t>Lecture 2.7</t>
-  </si>
-  <si>
-    <t>Lecture 1.5</t>
-  </si>
-  <si>
-    <t>UCB</t>
-  </si>
-  <si>
     <t>TS</t>
   </si>
   <si>
-    <t>Advanced</t>
-  </si>
-  <si>
     <t>Presentations</t>
   </si>
   <si>
@@ -138,9 +125,6 @@
     <t>Q&amp;A on R for final report</t>
   </si>
   <si>
-    <t>Fairness, contextual</t>
-  </si>
-  <si>
     <t>Contextual</t>
   </si>
   <si>
@@ -162,20 +146,26 @@
     <t>Lecture 2.6</t>
   </si>
   <si>
-    <t>Minor Learning from Big Data 2025</t>
-  </si>
-  <si>
     <t xml:space="preserve">UCB </t>
   </si>
   <si>
     <t xml:space="preserve">TS </t>
+  </si>
+  <si>
+    <t>Minor Learning from Big Data 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guest Lecture </t>
+  </si>
+  <si>
+    <t>UCB, Contextual, Fairness</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -231,6 +221,13 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -281,7 +278,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -297,9 +294,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -313,18 +307,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -336,6 +323,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -351,55 +339,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>88900</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>202050</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A2171122-447A-1F61-A4B2-AAD15D980EC4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="16598900" cy="11174850"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -718,21 +657,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{468B9219-EE8F-DF40-AC46-5CAF4ADF540B}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DB01412-0709-F441-A659-43EF7D79934F}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -742,8 +671,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
-        <v>40</v>
+      <c r="A1" s="15" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -767,38 +696,38 @@
       <c r="B5" s="2">
         <v>36</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="15" t="s">
-        <v>29</v>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="12" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>36</v>
       </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="21" t="s">
+      <c r="C6" s="8"/>
+      <c r="D6" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="15" t="s">
-        <v>30</v>
+      <c r="E6" s="8"/>
+      <c r="F6" s="12" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <v>36</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8" t="s">
+      <c r="C7" s="8"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="12" t="s">
         <v>8</v>
       </c>
     </row>
@@ -806,12 +735,12 @@
       <c r="B8" s="3">
         <v>36</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="23" t="s">
+      <c r="C8" s="9"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="F8" s="13" t="s">
         <v>8</v>
       </c>
     </row>
@@ -819,12 +748,12 @@
       <c r="B9" s="4">
         <v>37</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="17" t="s">
+      <c r="D9" s="10"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="14" t="s">
         <v>13</v>
       </c>
     </row>
@@ -832,12 +761,12 @@
       <c r="B10" s="2">
         <v>37</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="21" t="s">
+      <c r="C10" s="8"/>
+      <c r="D10" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="15" t="s">
+      <c r="E10" s="8"/>
+      <c r="F10" s="12" t="s">
         <v>13</v>
       </c>
     </row>
@@ -845,12 +774,12 @@
       <c r="B11" s="2">
         <v>37</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8" t="s">
+      <c r="C11" s="8"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="12" t="s">
         <v>14</v>
       </c>
     </row>
@@ -858,221 +787,204 @@
       <c r="B12" s="3">
         <v>37</v>
       </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="23" t="s">
+      <c r="C12" s="9"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="16" t="s">
-        <v>31</v>
+      <c r="F12" s="13" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="B13" s="4">
         <v>38</v>
       </c>
-      <c r="C13" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="17" t="s">
-        <v>26</v>
-      </c>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="14"/>
     </row>
     <row r="14" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="B14" s="2">
         <v>38</v>
       </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="15"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="12"/>
     </row>
     <row r="15" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="B15" s="2">
         <v>38</v>
       </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="15"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="12"/>
     </row>
     <row r="16" spans="1:6" ht="22" x14ac:dyDescent="0.3">
       <c r="B16" s="3">
         <v>38</v>
       </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="16"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="13"/>
     </row>
     <row r="17" spans="2:7" ht="22" x14ac:dyDescent="0.3">
       <c r="B17" s="4">
         <v>39</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="17" t="s">
-        <v>27</v>
+      <c r="D17" s="10"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="14" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="22" x14ac:dyDescent="0.3">
       <c r="B18" s="2">
         <v>39</v>
       </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="15"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="12"/>
     </row>
     <row r="19" spans="2:7" ht="22" x14ac:dyDescent="0.3">
       <c r="B19" s="2">
         <v>39</v>
       </c>
-      <c r="C19" s="9"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8" t="s">
+      <c r="C19" s="8"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F19" s="15" t="s">
-        <v>28</v>
+      <c r="F19" s="12" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="2:7" ht="22" x14ac:dyDescent="0.3">
       <c r="B20" s="3">
         <v>39</v>
       </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>28</v>
+      <c r="C20" s="9"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="2:7" ht="22" x14ac:dyDescent="0.3">
       <c r="B21" s="4">
         <v>40</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D21" s="11"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="17" t="s">
-        <v>24</v>
+      <c r="D21" s="10"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="14" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="22" x14ac:dyDescent="0.3">
       <c r="B22" s="2">
         <v>40</v>
       </c>
-      <c r="C22" s="9"/>
-      <c r="D22" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E22" s="9"/>
-      <c r="F22" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="G22" s="15"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="8"/>
+      <c r="F22" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G22" s="12"/>
     </row>
     <row r="23" spans="2:7" ht="22" x14ac:dyDescent="0.3">
       <c r="B23" s="2">
         <v>40</v>
       </c>
-      <c r="C23" s="9"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8" t="s">
+      <c r="C23" s="8"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F23" s="15" t="s">
-        <v>23</v>
+      <c r="F23" s="12" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="22" x14ac:dyDescent="0.3">
       <c r="B24" s="3">
         <v>40</v>
       </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="F24" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="G24" s="16"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="G24" s="13"/>
     </row>
     <row r="25" spans="2:7" ht="22" x14ac:dyDescent="0.3">
       <c r="B25" s="4">
         <v>41</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D25" s="11"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="17" t="s">
-        <v>32</v>
+      <c r="D25" s="10"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="14" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="2:7" ht="22" x14ac:dyDescent="0.3">
       <c r="B26" s="2">
         <v>41</v>
       </c>
-      <c r="C26" s="9"/>
-      <c r="D26" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="E26" s="9"/>
-      <c r="F26" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="G26" s="20"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="E26" s="8"/>
+      <c r="F26" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="G26" s="16"/>
     </row>
     <row r="27" spans="2:7" ht="22" x14ac:dyDescent="0.3">
       <c r="B27" s="2">
         <v>41</v>
       </c>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="F27" s="15" t="s">
-        <v>25</v>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="22" x14ac:dyDescent="0.3">
       <c r="B28" s="3">
         <v>41</v>
       </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="F28" s="16" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" ht="22" x14ac:dyDescent="0.3">
-      <c r="B29" s="7">
-        <v>42</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="18" t="s">
-        <v>26</v>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guiliberali/Library/Mobile Documents/com~apple~CloudDocs/Teaching /Teaching - BigData/Teach_BigData 2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guiliberali/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B8B5798-C910-044E-8D21-D32AAE337C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D54323-5439-5443-AB6A-F3BCF6EDA303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17480" xr2:uid="{16787138-0C24-184A-98B2-327E13C17B03}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
   <si>
     <t>Monday</t>
   </si>
@@ -159,6 +159,15 @@
   </si>
   <si>
     <t>UCB, Contextual, Fairness</t>
+  </si>
+  <si>
+    <t>Placeholder 1</t>
+  </si>
+  <si>
+    <t>Placeholder 2</t>
+  </si>
+  <si>
+    <t>By mid-august we will know if we will use this date</t>
   </si>
 </sst>
 </file>
@@ -661,12 +670,14 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="7.83203125" style="2" customWidth="1"/>
-    <col min="3" max="5" width="15.5" style="2" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" style="2" customWidth="1"/>
     <col min="6" max="6" width="42.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -987,6 +998,52 @@
         <v>27</v>
       </c>
     </row>
+    <row r="29" spans="2:7" ht="22" x14ac:dyDescent="0.3">
+      <c r="B29" s="4">
+        <v>42</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" s="10"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" ht="22" x14ac:dyDescent="0.3">
+      <c r="B30" s="2">
+        <v>42</v>
+      </c>
+      <c r="C30" s="8"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+    </row>
+    <row r="31" spans="2:7" ht="22" x14ac:dyDescent="0.3">
+      <c r="B31" s="2">
+        <v>42</v>
+      </c>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G31" s="16"/>
+    </row>
+    <row r="32" spans="2:7" ht="22" x14ac:dyDescent="0.3">
+      <c r="B32" s="3">
+        <v>42</v>
+      </c>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="13"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="75" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guiliberali/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guiliberali/Documents/GitHub/Learning-from-Big-Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D54323-5439-5443-AB6A-F3BCF6EDA303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A12B2782-E531-9748-A598-F42CE43B2F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17480" xr2:uid="{16787138-0C24-184A-98B2-327E13C17B03}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17460" xr2:uid="{16787138-0C24-184A-98B2-327E13C17B03}"/>
   </bookViews>
   <sheets>
     <sheet name="schedule" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">schedule!$A$1:$F$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">schedule!$A$1:$F$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
   <si>
     <t>Monday</t>
   </si>
@@ -159,15 +159,6 @@
   </si>
   <si>
     <t>UCB, Contextual, Fairness</t>
-  </si>
-  <si>
-    <t>Placeholder 1</t>
-  </si>
-  <si>
-    <t>Placeholder 2</t>
-  </si>
-  <si>
-    <t>By mid-august we will know if we will use this date</t>
   </si>
 </sst>
 </file>
@@ -670,7 +661,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
@@ -998,52 +989,6 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="2:7" ht="22" x14ac:dyDescent="0.3">
-      <c r="B29" s="4">
-        <v>42</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D29" s="10"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7" ht="22" x14ac:dyDescent="0.3">
-      <c r="B30" s="2">
-        <v>42</v>
-      </c>
-      <c r="C30" s="8"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
-    </row>
-    <row r="31" spans="2:7" ht="22" x14ac:dyDescent="0.3">
-      <c r="B31" s="2">
-        <v>42</v>
-      </c>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F31" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G31" s="16"/>
-    </row>
-    <row r="32" spans="2:7" ht="22" x14ac:dyDescent="0.3">
-      <c r="B32" s="3">
-        <v>42</v>
-      </c>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="13"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="75" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guiliberali/Documents/GitHub/Learning-from-Big-Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A12B2782-E531-9748-A598-F42CE43B2F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59A7CB95-82FC-BB46-9739-A86840F56B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17460" xr2:uid="{16787138-0C24-184A-98B2-327E13C17B03}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{16787138-0C24-184A-98B2-327E13C17B03}"/>
   </bookViews>
   <sheets>
     <sheet name="schedule" sheetId="1" r:id="rId1"/>
@@ -119,9 +119,6 @@
     <t xml:space="preserve">Intro </t>
   </si>
   <si>
-    <t>Intro - R, Rmarkdown, structure exercises</t>
-  </si>
-  <si>
     <t>Q&amp;A on R for final report</t>
   </si>
   <si>
@@ -159,6 +156,9 @@
   </si>
   <si>
     <t>UCB, Contextual, Fairness</t>
+  </si>
+  <si>
+    <t>Intro - R, LaTex, structure exercises</t>
   </si>
 </sst>
 </file>
@@ -674,7 +674,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -717,7 +717,7 @@
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="12" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="22" x14ac:dyDescent="0.3">
@@ -795,7 +795,7 @@
         <v>12</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="22" x14ac:dyDescent="0.3">
@@ -876,7 +876,7 @@
       <c r="C20" s="9"/>
       <c r="D20" s="18"/>
       <c r="E20" s="19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F20" s="12" t="s">
         <v>24</v>
@@ -901,11 +901,11 @@
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E22" s="8"/>
       <c r="F22" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G22" s="12"/>
     </row>
@@ -919,7 +919,7 @@
         <v>19</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="22" x14ac:dyDescent="0.3">
@@ -929,10 +929,10 @@
       <c r="C24" s="9"/>
       <c r="D24" s="18"/>
       <c r="E24" s="19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G24" s="13"/>
     </row>
@@ -946,7 +946,7 @@
       <c r="D25" s="10"/>
       <c r="E25" s="11"/>
       <c r="F25" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="2:7" ht="22" x14ac:dyDescent="0.3">
@@ -955,11 +955,11 @@
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E26" s="8"/>
       <c r="F26" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G26" s="16"/>
     </row>
@@ -970,7 +970,7 @@
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F27" s="20" t="s">
         <v>22</v>
@@ -983,10 +983,10 @@
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
